--- a/Sep_2026/daily Reports/OB PJP.xlsx
+++ b/Sep_2026/daily Reports/OB PJP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2652F9-BBCD-4517-807C-50FC83F84B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88624D2-0908-447B-A5D8-6E9D0F2C740A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1688,19 +1688,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1725,12 +1717,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1828,50 +1814,98 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1879,123 +1913,92 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2413,1383 +2416,1327 @@
   <dimension ref="A2:G81"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.90625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="17.90625" style="14" customWidth="1"/>
-    <col min="6" max="6" width="32.36328125" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="208.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.81640625" style="13"/>
+    <col min="1" max="1" width="11.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.90625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="17.90625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="32.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="208.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.81640625" style="9"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="121" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="62" t="s">
         <v>313</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="D4" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="46" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="69"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="53" t="s">
+      <c r="A5" s="60"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="66"/>
-      <c r="F5" s="54" t="s">
+      <c r="E5" s="69"/>
+      <c r="F5" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="49" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="69"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="53" t="s">
+      <c r="A6" s="60"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="66" t="s">
+      <c r="E6" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="49" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="69"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="53" t="s">
+      <c r="A7" s="60"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="54" t="s">
+      <c r="E7" s="69"/>
+      <c r="F7" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="55" t="s">
+      <c r="G7" s="49" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="69"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="53" t="s">
+      <c r="A8" s="60"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E8" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="56" t="s">
+      <c r="G8" s="50" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="70"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="57" t="s">
+      <c r="A9" s="61"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="66"/>
-      <c r="F9" s="58" t="s">
+      <c r="E9" s="69"/>
+      <c r="F9" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="59" t="s">
+      <c r="G9" s="53" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="77" t="s">
+      <c r="B10" s="63"/>
+      <c r="C10" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="66" t="s">
+      <c r="E10" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="60" t="s">
+      <c r="F10" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="61" t="s">
+      <c r="G10" s="55" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="69"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="53" t="s">
+      <c r="A11" s="60"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="62" t="s">
+      <c r="E11" s="69"/>
+      <c r="F11" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="63" t="s">
+      <c r="G11" s="57" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="69"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="53" t="s">
+      <c r="A12" s="60"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="66" t="s">
+      <c r="E12" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="55" t="s">
+      <c r="G12" s="49" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="69"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="53" t="s">
+      <c r="A13" s="60"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="66"/>
-      <c r="F13" s="62" t="s">
+      <c r="E13" s="69"/>
+      <c r="F13" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="55" t="s">
+      <c r="G13" s="49" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="69"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="53" t="s">
+      <c r="A14" s="60"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="66" t="s">
+      <c r="E14" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="62" t="s">
+      <c r="F14" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="57" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="70"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="57" t="s">
+      <c r="A15" s="61"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="67"/>
-      <c r="F15" s="64" t="s">
+      <c r="E15" s="73"/>
+      <c r="F15" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="59" t="s">
+      <c r="G15" s="53" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="62" t="s">
         <v>317</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="51" t="s">
+      <c r="F16" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="52" t="s">
+      <c r="G16" s="46" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="69"/>
-      <c r="B17" s="72"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="53" t="s">
+      <c r="A17" s="60"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="66"/>
-      <c r="F17" s="54" t="s">
+      <c r="E17" s="69"/>
+      <c r="F17" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="55" t="s">
+      <c r="G17" s="49" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="69"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="53" t="s">
+      <c r="A18" s="60"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="54" t="s">
+      <c r="F18" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="49" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="69"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="53" t="s">
+      <c r="A19" s="60"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="66"/>
-      <c r="F19" s="54" t="s">
+      <c r="E19" s="69"/>
+      <c r="F19" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="55" t="s">
+      <c r="G19" s="49" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="69"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="75"/>
-      <c r="D20" s="53" t="s">
+      <c r="A20" s="60"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="66" t="s">
+      <c r="E20" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="54" t="s">
+      <c r="F20" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="G20" s="56" t="s">
+      <c r="G20" s="50" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="70"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="76"/>
-      <c r="D21" s="57" t="s">
+      <c r="A21" s="61"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="66"/>
-      <c r="F21" s="58" t="s">
+      <c r="E21" s="69"/>
+      <c r="F21" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="G21" s="59" t="s">
+      <c r="G21" s="53" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="77" t="s">
+      <c r="B22" s="63"/>
+      <c r="C22" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D22" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="66" t="s">
+      <c r="E22" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="60" t="s">
+      <c r="F22" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="61" t="s">
+      <c r="G22" s="55" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="69"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="53" t="s">
+      <c r="A23" s="60"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="66"/>
-      <c r="F23" s="62" t="s">
+      <c r="E23" s="69"/>
+      <c r="F23" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="G23" s="63" t="s">
+      <c r="G23" s="57" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="69"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="53" t="s">
+      <c r="A24" s="60"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="66" t="s">
+      <c r="E24" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="62" t="s">
+      <c r="F24" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="G24" s="55" t="s">
+      <c r="G24" s="49" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="69"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="53" t="s">
+      <c r="A25" s="60"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="66"/>
-      <c r="F25" s="62" t="s">
+      <c r="E25" s="69"/>
+      <c r="F25" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="55" t="s">
+      <c r="G25" s="49" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="69"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="53" t="s">
+      <c r="A26" s="60"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="66" t="s">
+      <c r="E26" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="62" t="s">
+      <c r="F26" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="G26" s="63" t="s">
+      <c r="G26" s="57" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="70"/>
-      <c r="B27" s="73"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="57" t="s">
+      <c r="A27" s="61"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="67"/>
-      <c r="F27" s="64" t="s">
+      <c r="E27" s="73"/>
+      <c r="F27" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="G27" s="59" t="s">
+      <c r="G27" s="53" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="68" t="s">
+      <c r="A28" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="71" t="s">
+      <c r="B28" s="62" t="s">
         <v>191</v>
       </c>
-      <c r="C28" s="74" t="s">
+      <c r="C28" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="50" t="s">
+      <c r="D28" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="51" t="s">
+      <c r="F28" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="52" t="s">
+      <c r="G28" s="46" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="69"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="53" t="s">
+      <c r="A29" s="60"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="66"/>
-      <c r="F29" s="54" t="s">
+      <c r="E29" s="69"/>
+      <c r="F29" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="G29" s="55" t="s">
+      <c r="G29" s="49" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="69"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="75"/>
-      <c r="D30" s="53" t="s">
+      <c r="A30" s="60"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="66" t="s">
+      <c r="E30" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="54" t="s">
+      <c r="F30" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="G30" s="55" t="s">
+      <c r="G30" s="49" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="69"/>
-      <c r="B31" s="72"/>
-      <c r="C31" s="75"/>
-      <c r="D31" s="53" t="s">
+      <c r="A31" s="60"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="66"/>
-      <c r="F31" s="54" t="s">
+      <c r="E31" s="69"/>
+      <c r="F31" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="55" t="s">
+      <c r="G31" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="69"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="75"/>
-      <c r="D32" s="53" t="s">
+      <c r="A32" s="60"/>
+      <c r="B32" s="63"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="66" t="s">
+      <c r="E32" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="54" t="s">
+      <c r="F32" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="G32" s="56" t="s">
+      <c r="G32" s="50" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="70"/>
-      <c r="B33" s="72"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="57" t="s">
+      <c r="A33" s="61"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="66"/>
-      <c r="F33" s="58" t="s">
+      <c r="E33" s="69"/>
+      <c r="F33" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="G33" s="59" t="s">
+      <c r="G33" s="53" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="68" t="s">
+      <c r="A34" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="72"/>
-      <c r="C34" s="77" t="s">
+      <c r="B34" s="63"/>
+      <c r="C34" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="D34" s="50" t="s">
+      <c r="D34" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="66" t="s">
+      <c r="E34" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="F34" s="60" t="s">
+      <c r="F34" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="G34" s="61" t="s">
+      <c r="G34" s="55" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="69"/>
-      <c r="B35" s="72"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="53" t="s">
+      <c r="A35" s="60"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="66"/>
-      <c r="F35" s="62" t="s">
+      <c r="E35" s="69"/>
+      <c r="F35" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="G35" s="63" t="s">
+      <c r="G35" s="57" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="69"/>
-      <c r="B36" s="72"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="53" t="s">
+      <c r="A36" s="60"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="66" t="s">
+      <c r="E36" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F36" s="62" t="s">
+      <c r="F36" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="55" t="s">
+      <c r="G36" s="49" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="69"/>
-      <c r="B37" s="72"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="53" t="s">
+      <c r="A37" s="60"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="71"/>
+      <c r="D37" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="66"/>
-      <c r="F37" s="62" t="s">
+      <c r="E37" s="69"/>
+      <c r="F37" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="G37" s="55" t="s">
+      <c r="G37" s="49" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="69"/>
-      <c r="B38" s="72"/>
-      <c r="C38" s="78"/>
-      <c r="D38" s="53" t="s">
+      <c r="A38" s="60"/>
+      <c r="B38" s="63"/>
+      <c r="C38" s="71"/>
+      <c r="D38" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="66" t="s">
+      <c r="E38" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="62" t="s">
+      <c r="F38" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="G38" s="63" t="s">
+      <c r="G38" s="57" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="70"/>
-      <c r="B39" s="73"/>
-      <c r="C39" s="79"/>
-      <c r="D39" s="57" t="s">
+      <c r="A39" s="61"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="67"/>
-      <c r="F39" s="64" t="s">
+      <c r="E39" s="73"/>
+      <c r="F39" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="G39" s="59" t="s">
+      <c r="G39" s="53" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="68" t="s">
+      <c r="A40" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="71" t="s">
+      <c r="B40" s="62" t="s">
         <v>300</v>
       </c>
-      <c r="C40" s="74" t="s">
+      <c r="C40" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="50" t="s">
+      <c r="D40" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="65" t="s">
+      <c r="E40" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F40" s="51" t="s">
+      <c r="F40" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="G40" s="52" t="s">
+      <c r="G40" s="46" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="69"/>
-      <c r="B41" s="72"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="53" t="s">
+      <c r="A41" s="60"/>
+      <c r="B41" s="63"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="66"/>
-      <c r="F41" s="54" t="s">
+      <c r="E41" s="69"/>
+      <c r="F41" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="G41" s="55" t="s">
+      <c r="G41" s="49" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="69"/>
-      <c r="B42" s="72"/>
-      <c r="C42" s="75"/>
-      <c r="D42" s="53" t="s">
+      <c r="A42" s="60"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="66" t="s">
+      <c r="E42" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F42" s="54" t="s">
+      <c r="F42" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="G42" s="55" t="s">
+      <c r="G42" s="49" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="69"/>
-      <c r="B43" s="72"/>
-      <c r="C43" s="75"/>
-      <c r="D43" s="53" t="s">
+      <c r="A43" s="60"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="65"/>
+      <c r="D43" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E43" s="66"/>
-      <c r="F43" s="54" t="s">
+      <c r="E43" s="69"/>
+      <c r="F43" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="G43" s="55" t="s">
+      <c r="G43" s="49" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="69"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="75"/>
-      <c r="D44" s="53" t="s">
+      <c r="A44" s="60"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="66" t="s">
+      <c r="E44" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F44" s="54" t="s">
+      <c r="F44" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="G44" s="56" t="s">
+      <c r="G44" s="50" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A45" s="70"/>
-      <c r="B45" s="72"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="57" t="s">
+      <c r="A45" s="61"/>
+      <c r="B45" s="63"/>
+      <c r="C45" s="66"/>
+      <c r="D45" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E45" s="66"/>
-      <c r="F45" s="58" t="s">
+      <c r="E45" s="69"/>
+      <c r="F45" s="52" t="s">
         <v>105</v>
       </c>
-      <c r="G45" s="59" t="s">
+      <c r="G45" s="53" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="B46" s="72"/>
-      <c r="C46" s="77" t="s">
+      <c r="B46" s="63"/>
+      <c r="C46" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="50" t="s">
+      <c r="D46" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E46" s="66" t="s">
+      <c r="E46" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="F46" s="60" t="s">
+      <c r="F46" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="G46" s="61" t="s">
+      <c r="G46" s="55" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="69"/>
-      <c r="B47" s="72"/>
-      <c r="C47" s="78"/>
-      <c r="D47" s="53" t="s">
+      <c r="A47" s="60"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="66"/>
-      <c r="F47" s="62" t="s">
+      <c r="E47" s="69"/>
+      <c r="F47" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="G47" s="63" t="s">
+      <c r="G47" s="57" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="69"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="53" t="s">
+      <c r="A48" s="60"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="71"/>
+      <c r="D48" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="66" t="s">
+      <c r="E48" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F48" s="62" t="s">
+      <c r="F48" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="G48" s="55" t="s">
+      <c r="G48" s="49" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="69"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="78"/>
-      <c r="D49" s="53" t="s">
+      <c r="A49" s="60"/>
+      <c r="B49" s="63"/>
+      <c r="C49" s="71"/>
+      <c r="D49" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="66"/>
-      <c r="F49" s="62" t="s">
+      <c r="E49" s="69"/>
+      <c r="F49" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="G49" s="55" t="s">
+      <c r="G49" s="49" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="69"/>
-      <c r="B50" s="72"/>
-      <c r="C50" s="78"/>
-      <c r="D50" s="53" t="s">
+      <c r="A50" s="60"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="71"/>
+      <c r="D50" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="66" t="s">
+      <c r="E50" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="62" t="s">
+      <c r="F50" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="G50" s="63" t="s">
+      <c r="G50" s="57" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A51" s="70"/>
-      <c r="B51" s="73"/>
-      <c r="C51" s="79"/>
-      <c r="D51" s="57" t="s">
+      <c r="A51" s="61"/>
+      <c r="B51" s="67"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E51" s="67"/>
-      <c r="F51" s="64" t="s">
+      <c r="E51" s="73"/>
+      <c r="F51" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="G51" s="59" t="s">
+      <c r="G51" s="53" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="68" t="s">
+      <c r="A52" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="B52" s="71" t="s">
+      <c r="B52" s="62" t="s">
         <v>312</v>
       </c>
-      <c r="C52" s="74" t="s">
+      <c r="C52" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="50" t="s">
+      <c r="D52" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="65" t="s">
+      <c r="E52" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="51" t="s">
+      <c r="F52" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="G52" s="52" t="s">
+      <c r="G52" s="46" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="69"/>
-      <c r="B53" s="72"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="53" t="s">
+      <c r="A53" s="60"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="65"/>
+      <c r="D53" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="66"/>
-      <c r="F53" s="54" t="s">
+      <c r="E53" s="69"/>
+      <c r="F53" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="G53" s="55" t="s">
+      <c r="G53" s="49" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="69"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="75"/>
-      <c r="D54" s="53" t="s">
+      <c r="A54" s="60"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="66" t="s">
+      <c r="E54" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F54" s="54" t="s">
+      <c r="F54" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="55" t="s">
+      <c r="G54" s="49" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="69"/>
-      <c r="B55" s="72"/>
-      <c r="C55" s="75"/>
-      <c r="D55" s="53" t="s">
+      <c r="A55" s="60"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="65"/>
+      <c r="D55" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E55" s="66"/>
-      <c r="F55" s="54" t="s">
+      <c r="E55" s="69"/>
+      <c r="F55" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="G55" s="55" t="s">
+      <c r="G55" s="49" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="69"/>
-      <c r="B56" s="72"/>
-      <c r="C56" s="75"/>
-      <c r="D56" s="53" t="s">
+      <c r="A56" s="60"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="66" t="s">
+      <c r="E56" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F56" s="54" t="s">
+      <c r="F56" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="G56" s="56" t="s">
+      <c r="G56" s="50" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A57" s="70"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="76"/>
-      <c r="D57" s="57" t="s">
+      <c r="A57" s="61"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E57" s="66"/>
-      <c r="F57" s="58" t="s">
+      <c r="E57" s="69"/>
+      <c r="F57" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="G57" s="59" t="s">
+      <c r="G57" s="53" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="68" t="s">
+      <c r="A58" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="72"/>
-      <c r="C58" s="77" t="s">
+      <c r="B58" s="63"/>
+      <c r="C58" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="50" t="s">
+      <c r="D58" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="66" t="s">
+      <c r="E58" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="F58" s="60" t="s">
+      <c r="F58" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="55" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="69"/>
-      <c r="B59" s="72"/>
-      <c r="C59" s="78"/>
-      <c r="D59" s="53" t="s">
+      <c r="A59" s="60"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="71"/>
+      <c r="D59" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="66"/>
-      <c r="F59" s="62" t="s">
+      <c r="E59" s="69"/>
+      <c r="F59" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="G59" s="63" t="s">
+      <c r="G59" s="57" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="69"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="78"/>
-      <c r="D60" s="53" t="s">
+      <c r="A60" s="60"/>
+      <c r="B60" s="63"/>
+      <c r="C60" s="71"/>
+      <c r="D60" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E60" s="66" t="s">
+      <c r="E60" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F60" s="62" t="s">
+      <c r="F60" s="56" t="s">
         <v>141</v>
       </c>
-      <c r="G60" s="55" t="s">
+      <c r="G60" s="49" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="69"/>
-      <c r="B61" s="72"/>
-      <c r="C61" s="78"/>
-      <c r="D61" s="53" t="s">
+      <c r="A61" s="60"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E61" s="66"/>
-      <c r="F61" s="62" t="s">
+      <c r="E61" s="69"/>
+      <c r="F61" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="G61" s="55" t="s">
+      <c r="G61" s="49" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="69"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="78"/>
-      <c r="D62" s="53" t="s">
+      <c r="A62" s="60"/>
+      <c r="B62" s="63"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E62" s="66" t="s">
+      <c r="E62" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="F62" s="62" t="s">
+      <c r="F62" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="G62" s="63" t="s">
+      <c r="G62" s="57" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A63" s="70"/>
-      <c r="B63" s="73"/>
-      <c r="C63" s="79"/>
-      <c r="D63" s="57" t="s">
+      <c r="A63" s="61"/>
+      <c r="B63" s="67"/>
+      <c r="C63" s="72"/>
+      <c r="D63" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E63" s="67"/>
-      <c r="F63" s="64" t="s">
+      <c r="E63" s="73"/>
+      <c r="F63" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="G63" s="59" t="s">
+      <c r="G63" s="53" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="68" t="s">
+      <c r="A64" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="B64" s="71" t="s">
+      <c r="B64" s="62" t="s">
         <v>314</v>
       </c>
-      <c r="C64" s="74" t="s">
+      <c r="C64" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="D64" s="50" t="s">
+      <c r="D64" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E64" s="65" t="s">
+      <c r="E64" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="51" t="s">
+      <c r="F64" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="G64" s="52" t="s">
+      <c r="G64" s="46" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="69"/>
-      <c r="B65" s="72"/>
-      <c r="C65" s="75"/>
-      <c r="D65" s="53" t="s">
+      <c r="A65" s="60"/>
+      <c r="B65" s="63"/>
+      <c r="C65" s="65"/>
+      <c r="D65" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="66"/>
-      <c r="F65" s="54" t="s">
+      <c r="E65" s="69"/>
+      <c r="F65" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="G65" s="55" t="s">
+      <c r="G65" s="49" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="69"/>
-      <c r="B66" s="72"/>
-      <c r="C66" s="75"/>
-      <c r="D66" s="53" t="s">
+      <c r="A66" s="60"/>
+      <c r="B66" s="63"/>
+      <c r="C66" s="65"/>
+      <c r="D66" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E66" s="66" t="s">
+      <c r="E66" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F66" s="54" t="s">
+      <c r="F66" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="G66" s="55" t="s">
+      <c r="G66" s="49" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="69"/>
-      <c r="B67" s="72"/>
-      <c r="C67" s="75"/>
-      <c r="D67" s="53" t="s">
+      <c r="A67" s="60"/>
+      <c r="B67" s="63"/>
+      <c r="C67" s="65"/>
+      <c r="D67" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E67" s="66"/>
-      <c r="F67" s="54" t="s">
+      <c r="E67" s="69"/>
+      <c r="F67" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="G67" s="55" t="s">
+      <c r="G67" s="49" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="69"/>
-      <c r="B68" s="72"/>
-      <c r="C68" s="75"/>
-      <c r="D68" s="53" t="s">
+      <c r="A68" s="60"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="65"/>
+      <c r="D68" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="66" t="s">
+      <c r="E68" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F68" s="54" t="s">
+      <c r="F68" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="G68" s="56" t="s">
+      <c r="G68" s="50" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A69" s="70"/>
-      <c r="B69" s="72"/>
-      <c r="C69" s="76"/>
-      <c r="D69" s="57" t="s">
+      <c r="A69" s="61"/>
+      <c r="B69" s="63"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E69" s="66"/>
-      <c r="F69" s="58" t="s">
+      <c r="E69" s="69"/>
+      <c r="F69" s="52" t="s">
         <v>160</v>
       </c>
-      <c r="G69" s="59" t="s">
+      <c r="G69" s="53" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="68" t="s">
+      <c r="A70" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="B70" s="72"/>
-      <c r="C70" s="77" t="s">
+      <c r="B70" s="63"/>
+      <c r="C70" s="70" t="s">
         <v>163</v>
       </c>
-      <c r="D70" s="50" t="s">
+      <c r="D70" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E70" s="66" t="s">
+      <c r="E70" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="F70" s="60" t="s">
+      <c r="F70" s="54" t="s">
         <v>164</v>
       </c>
-      <c r="G70" s="61" t="s">
+      <c r="G70" s="55" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="69"/>
-      <c r="B71" s="72"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="53" t="s">
+      <c r="A71" s="60"/>
+      <c r="B71" s="63"/>
+      <c r="C71" s="71"/>
+      <c r="D71" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E71" s="66"/>
-      <c r="F71" s="62" t="s">
+      <c r="E71" s="69"/>
+      <c r="F71" s="56" t="s">
         <v>166</v>
       </c>
-      <c r="G71" s="63" t="s">
+      <c r="G71" s="57" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="69"/>
-      <c r="B72" s="72"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="53" t="s">
+      <c r="A72" s="60"/>
+      <c r="B72" s="63"/>
+      <c r="C72" s="71"/>
+      <c r="D72" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="66" t="s">
+      <c r="E72" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F72" s="62" t="s">
+      <c r="F72" s="56" t="s">
         <v>168</v>
       </c>
-      <c r="G72" s="55" t="s">
+      <c r="G72" s="49" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="69"/>
-      <c r="B73" s="72"/>
-      <c r="C73" s="78"/>
-      <c r="D73" s="53" t="s">
+      <c r="A73" s="60"/>
+      <c r="B73" s="63"/>
+      <c r="C73" s="71"/>
+      <c r="D73" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E73" s="66"/>
-      <c r="F73" s="62" t="s">
+      <c r="E73" s="69"/>
+      <c r="F73" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="G73" s="55" t="s">
+      <c r="G73" s="49" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="69"/>
-      <c r="B74" s="72"/>
-      <c r="C74" s="78"/>
-      <c r="D74" s="53" t="s">
+      <c r="A74" s="60"/>
+      <c r="B74" s="63"/>
+      <c r="C74" s="71"/>
+      <c r="D74" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E74" s="66" t="s">
+      <c r="E74" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="62" t="s">
+      <c r="F74" s="56" t="s">
         <v>172</v>
       </c>
-      <c r="G74" s="63" t="s">
+      <c r="G74" s="57" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A75" s="70"/>
-      <c r="B75" s="73"/>
-      <c r="C75" s="79"/>
-      <c r="D75" s="57" t="s">
+      <c r="A75" s="61"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E75" s="67"/>
-      <c r="F75" s="64" t="s">
+      <c r="E75" s="73"/>
+      <c r="F75" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="G75" s="59" t="s">
+      <c r="G75" s="53" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="68" t="s">
+      <c r="A76" s="59" t="s">
         <v>188</v>
       </c>
-      <c r="B76" s="71">
+      <c r="B76" s="62">
         <v>7</v>
       </c>
-      <c r="C76" s="74" t="s">
+      <c r="C76" s="64" t="s">
         <v>189</v>
       </c>
-      <c r="D76" s="50" t="s">
+      <c r="D76" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E76" s="65"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="52"/>
+      <c r="E76" s="68"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="46"/>
     </row>
     <row r="77" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="69"/>
-      <c r="B77" s="72"/>
-      <c r="C77" s="75"/>
-      <c r="D77" s="53" t="s">
+      <c r="A77" s="60"/>
+      <c r="B77" s="63"/>
+      <c r="C77" s="65"/>
+      <c r="D77" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E77" s="66"/>
-      <c r="F77" s="54"/>
-      <c r="G77" s="55"/>
+      <c r="E77" s="69"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="49"/>
     </row>
     <row r="78" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="69"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="75"/>
-      <c r="D78" s="53" t="s">
+      <c r="A78" s="60"/>
+      <c r="B78" s="63"/>
+      <c r="C78" s="65"/>
+      <c r="D78" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E78" s="66"/>
-      <c r="F78" s="54"/>
-      <c r="G78" s="55"/>
+      <c r="E78" s="69"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="49"/>
     </row>
     <row r="79" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="69"/>
-      <c r="B79" s="72"/>
-      <c r="C79" s="75"/>
-      <c r="D79" s="53" t="s">
+      <c r="A79" s="60"/>
+      <c r="B79" s="63"/>
+      <c r="C79" s="65"/>
+      <c r="D79" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E79" s="66"/>
-      <c r="F79" s="54"/>
-      <c r="G79" s="55"/>
+      <c r="E79" s="69"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="49"/>
     </row>
     <row r="80" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="69"/>
-      <c r="B80" s="72"/>
-      <c r="C80" s="75"/>
-      <c r="D80" s="53" t="s">
+      <c r="A80" s="60"/>
+      <c r="B80" s="63"/>
+      <c r="C80" s="65"/>
+      <c r="D80" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="E80" s="66"/>
-      <c r="F80" s="54"/>
-      <c r="G80" s="56"/>
+      <c r="E80" s="69"/>
+      <c r="F80" s="48"/>
+      <c r="G80" s="50"/>
     </row>
     <row r="81" spans="1:7" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A81" s="70"/>
-      <c r="B81" s="72"/>
-      <c r="C81" s="76"/>
-      <c r="D81" s="57" t="s">
+      <c r="A81" s="61"/>
+      <c r="B81" s="63"/>
+      <c r="C81" s="66"/>
+      <c r="D81" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E81" s="66"/>
-      <c r="F81" s="58"/>
-      <c r="G81" s="59"/>
+      <c r="E81" s="69"/>
+      <c r="F81" s="52"/>
+      <c r="G81" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="B76:B81"/>
-    <mergeCell ref="C76:C81"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="C64:C69"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="E66:E67"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="C70:C75"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="B52:B63"/>
-    <mergeCell ref="C52:C57"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="A58:A63"/>
-    <mergeCell ref="C58:C63"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B40:B51"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="C46:C51"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="B16:B27"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
     <mergeCell ref="E76:E77"/>
     <mergeCell ref="E78:E79"/>
     <mergeCell ref="E80:E81"/>
@@ -3806,6 +3753,62 @@
     <mergeCell ref="E46:E47"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="E50:E51"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="C28:C33"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="C34:C39"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="B40:B51"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="B52:B63"/>
+    <mergeCell ref="C52:C57"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="C58:C63"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="C70:C75"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="B76:B81"/>
+    <mergeCell ref="C76:C81"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="C64:C69"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:F9 F16:F21 F28:F33 F40:F45 F52:F57 F64:F69 F76:F81">
     <cfRule type="duplicateValues" dxfId="12" priority="18"/>
@@ -3827,14 +3830,14 @@
   <dimension ref="A2:G63"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.453125" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="118.7265625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.81640625" style="13"/>
+    <col min="1" max="1" width="7.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.81640625" style="9"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -3842,1037 +3845,1082 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24" t="s">
+      <c r="E3" s="17"/>
+      <c r="F3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="19" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="80" t="s">
+      <c r="A4" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="107" t="s">
         <v>310</v>
       </c>
-      <c r="C4" s="83" t="s">
+      <c r="C4" s="114" t="s">
         <v>301</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="2" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="81"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="40" t="s">
+      <c r="A5" s="91"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="41" t="s">
+      <c r="E5" s="106"/>
+      <c r="F5" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="3" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="81"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="40" t="s">
+      <c r="A6" s="91"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="87" t="s">
+      <c r="E6" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="35" t="s">
         <v>196</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="3" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="81"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="40" t="s">
+      <c r="A7" s="91"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="111"/>
+      <c r="D7" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="87"/>
-      <c r="F7" s="41" t="s">
+      <c r="E7" s="106"/>
+      <c r="F7" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="3" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="81"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="40" t="s">
+      <c r="A8" s="91"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="87" t="s">
+      <c r="E8" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="3" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="82"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="42" t="s">
+      <c r="A9" s="95"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="87"/>
-      <c r="F9" s="43" t="s">
+      <c r="E9" s="106"/>
+      <c r="F9" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="5" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="91" t="s">
+      <c r="A10" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="89"/>
-      <c r="C10" s="84" t="s">
+      <c r="B10" s="108"/>
+      <c r="C10" s="111" t="s">
         <v>302</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="87" t="s">
+      <c r="E10" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="81"/>
-      <c r="B11" s="89"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="40" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="87"/>
-      <c r="F11" s="46" t="s">
+      <c r="E11" s="106"/>
+      <c r="F11" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="81"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="40" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="108"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="87" t="s">
+      <c r="E12" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="3" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="81"/>
-      <c r="B13" s="89"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="40" t="s">
+      <c r="A13" s="91"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="87"/>
-      <c r="F13" s="46" t="s">
+      <c r="E13" s="106"/>
+      <c r="F13" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="3" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="81"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="40" t="s">
+      <c r="A14" s="91"/>
+      <c r="B14" s="108"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="87" t="s">
+      <c r="E14" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="3" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="82"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="42" t="s">
+      <c r="A15" s="95"/>
+      <c r="B15" s="109"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="92"/>
-      <c r="F15" s="43" t="s">
+      <c r="E15" s="113"/>
+      <c r="F15" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="5" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="107" t="s">
         <v>311</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="111" t="s">
         <v>303</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="86" t="s">
+      <c r="E16" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="35" t="s">
         <v>216</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="81"/>
-      <c r="B17" s="89"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="40" t="s">
+      <c r="A17" s="91"/>
+      <c r="B17" s="108"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="87"/>
-      <c r="F17" s="46" t="s">
+      <c r="E17" s="106"/>
+      <c r="F17" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="6" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="81"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="40" t="s">
+      <c r="A18" s="91"/>
+      <c r="B18" s="108"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="87" t="s">
+      <c r="E18" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="3" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="81"/>
-      <c r="B19" s="89"/>
-      <c r="C19" s="84"/>
-      <c r="D19" s="40" t="s">
+      <c r="A19" s="91"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="87"/>
-      <c r="F19" s="46" t="s">
+      <c r="E19" s="106"/>
+      <c r="F19" s="40" t="s">
         <v>222</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="3" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="81"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="40" t="s">
+      <c r="A20" s="91"/>
+      <c r="B20" s="108"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="87" t="s">
+      <c r="E20" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="46" t="s">
+      <c r="F20" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="3" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="82"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="42" t="s">
+      <c r="A21" s="95"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="87"/>
-      <c r="F21" s="43" t="s">
+      <c r="E21" s="106"/>
+      <c r="F21" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="5" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="89"/>
-      <c r="C22" s="84" t="s">
+      <c r="B22" s="108"/>
+      <c r="C22" s="111" t="s">
         <v>305</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="87" t="s">
+      <c r="E22" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="45" t="s">
+      <c r="F22" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="7" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="81"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="40" t="s">
+      <c r="A23" s="91"/>
+      <c r="B23" s="108"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="87"/>
-      <c r="F23" s="46" t="s">
+      <c r="E23" s="106"/>
+      <c r="F23" s="40" t="s">
         <v>230</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="6" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="81"/>
-      <c r="B24" s="89"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="40" t="s">
+      <c r="A24" s="91"/>
+      <c r="B24" s="108"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E24" s="87" t="s">
+      <c r="E24" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="46" t="s">
+      <c r="F24" s="40" t="s">
         <v>232</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="6" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="81"/>
-      <c r="B25" s="89"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="40" t="s">
+      <c r="A25" s="91"/>
+      <c r="B25" s="108"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="87"/>
-      <c r="F25" s="46" t="s">
+      <c r="E25" s="106"/>
+      <c r="F25" s="40" t="s">
         <v>234</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="3" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="81"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="40" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="108"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="87" t="s">
+      <c r="E26" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="F26" s="46" t="s">
+      <c r="F26" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="3" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="82"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="42" t="s">
+      <c r="A27" s="95"/>
+      <c r="B27" s="109"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="92"/>
-      <c r="F27" s="43" t="s">
+      <c r="E27" s="113"/>
+      <c r="F27" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="5" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="107" t="s">
         <v>311</v>
       </c>
-      <c r="C28" s="94" t="s">
+      <c r="C28" s="102" t="s">
         <v>304</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="86" t="s">
+      <c r="E28" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="2" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="81"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="95"/>
-      <c r="D29" s="40" t="s">
+      <c r="A29" s="91"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="87"/>
-      <c r="F29" s="46" t="s">
+      <c r="E29" s="106"/>
+      <c r="F29" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="81"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="95"/>
-      <c r="D30" s="40" t="s">
+      <c r="A30" s="91"/>
+      <c r="B30" s="108"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="87" t="s">
+      <c r="E30" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="46" t="s">
+      <c r="F30" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="6" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="81"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="95"/>
-      <c r="D31" s="40" t="s">
+      <c r="A31" s="91"/>
+      <c r="B31" s="108"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="87"/>
-      <c r="F31" s="46" t="s">
+      <c r="E31" s="106"/>
+      <c r="F31" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="3" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="81"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="95"/>
-      <c r="D32" s="40" t="s">
+      <c r="A32" s="91"/>
+      <c r="B32" s="108"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="87" t="s">
+      <c r="E32" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="46" t="s">
+      <c r="F32" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="3" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="93"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="48" t="s">
+      <c r="A33" s="97"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="87"/>
-      <c r="F33" s="49" t="s">
+      <c r="E33" s="106"/>
+      <c r="F33" s="43" t="s">
         <v>250</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="8" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="80" t="s">
+      <c r="A34" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="103" t="s">
+      <c r="B34" s="100" t="s">
         <v>316</v>
       </c>
-      <c r="C34" s="97" t="s">
+      <c r="C34" s="92" t="s">
         <v>306</v>
       </c>
-      <c r="D34" s="26" t="s">
+      <c r="D34" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="100" t="s">
+      <c r="E34" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="13" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="81"/>
-      <c r="B35" s="103"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="28" t="s">
+      <c r="A35" s="91"/>
+      <c r="B35" s="100"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="101"/>
-      <c r="F35" s="29" t="s">
+      <c r="E35" s="81"/>
+      <c r="F35" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="81"/>
-      <c r="B36" s="103"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="28" t="s">
+      <c r="A36" s="91"/>
+      <c r="B36" s="100"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E36" s="101" t="s">
+      <c r="E36" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="6" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="81"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="28" t="s">
+      <c r="A37" s="91"/>
+      <c r="B37" s="100"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="101"/>
-      <c r="F37" s="29" t="s">
+      <c r="E37" s="81"/>
+      <c r="F37" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="6" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="81"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="28" t="s">
+      <c r="A38" s="91"/>
+      <c r="B38" s="100"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="101" t="s">
+      <c r="E38" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="6" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="93"/>
-      <c r="B39" s="104"/>
-      <c r="C39" s="99"/>
-      <c r="D39" s="30" t="s">
+      <c r="A39" s="97"/>
+      <c r="B39" s="101"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="102"/>
-      <c r="F39" s="31" t="s">
+      <c r="E39" s="99"/>
+      <c r="F39" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="G39" s="16" t="s">
+      <c r="G39" s="12" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="B40" s="105" t="s">
+      <c r="B40" s="82" t="s">
         <v>315</v>
       </c>
-      <c r="C40" s="97" t="s">
+      <c r="C40" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D40" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="100" t="s">
+      <c r="E40" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="F40" s="32" t="s">
+      <c r="F40" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="2" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="81"/>
-      <c r="B41" s="106"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="28" t="s">
+      <c r="A41" s="91"/>
+      <c r="B41" s="83"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="101"/>
-      <c r="F41" s="29" t="s">
+      <c r="E41" s="81"/>
+      <c r="F41" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="6" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="81"/>
-      <c r="B42" s="106"/>
-      <c r="C42" s="98"/>
-      <c r="D42" s="28" t="s">
+      <c r="A42" s="91"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="93"/>
+      <c r="D42" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="101" t="s">
+      <c r="E42" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="6" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="81"/>
-      <c r="B43" s="106"/>
-      <c r="C43" s="98"/>
-      <c r="D43" s="28" t="s">
+      <c r="A43" s="91"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="93"/>
+      <c r="D43" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E43" s="101"/>
-      <c r="F43" s="29" t="s">
+      <c r="E43" s="81"/>
+      <c r="F43" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="6" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="81"/>
-      <c r="B44" s="106"/>
-      <c r="C44" s="98"/>
-      <c r="D44" s="28" t="s">
+      <c r="A44" s="91"/>
+      <c r="B44" s="83"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="101" t="s">
+      <c r="E44" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="F44" s="33" t="s">
+      <c r="F44" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="3" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="81"/>
-      <c r="B45" s="106"/>
-      <c r="C45" s="98"/>
-      <c r="D45" s="28" t="s">
+      <c r="A45" s="91"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E45" s="101"/>
-      <c r="F45" s="29" t="s">
+      <c r="E45" s="81"/>
+      <c r="F45" s="23" t="s">
         <v>274</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="6" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="81" t="s">
+      <c r="A46" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="B46" s="106"/>
-      <c r="C46" s="98" t="s">
+      <c r="B46" s="83"/>
+      <c r="C46" s="93" t="s">
         <v>276</v>
       </c>
-      <c r="D46" s="28" t="s">
+      <c r="D46" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="E46" s="101" t="s">
+      <c r="E46" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="29" t="s">
+      <c r="F46" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G46" s="3" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="81"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="98"/>
-      <c r="D47" s="28" t="s">
+      <c r="A47" s="91"/>
+      <c r="B47" s="83"/>
+      <c r="C47" s="93"/>
+      <c r="D47" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="101"/>
-      <c r="F47" s="29" t="s">
+      <c r="E47" s="81"/>
+      <c r="F47" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="6" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="81"/>
-      <c r="B48" s="106"/>
-      <c r="C48" s="98"/>
-      <c r="D48" s="28" t="s">
+      <c r="A48" s="91"/>
+      <c r="B48" s="83"/>
+      <c r="C48" s="93"/>
+      <c r="D48" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="101" t="s">
+      <c r="E48" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="29" t="s">
+      <c r="F48" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="6" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
-      <c r="B49" s="106"/>
-      <c r="C49" s="98"/>
-      <c r="D49" s="28" t="s">
+      <c r="A49" s="91"/>
+      <c r="B49" s="83"/>
+      <c r="C49" s="93"/>
+      <c r="D49" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="101"/>
-      <c r="F49" s="29" t="s">
+      <c r="E49" s="81"/>
+      <c r="F49" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="6" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="81"/>
-      <c r="B50" s="106"/>
-      <c r="C50" s="98"/>
-      <c r="D50" s="28" t="s">
+      <c r="A50" s="91"/>
+      <c r="B50" s="83"/>
+      <c r="C50" s="93"/>
+      <c r="D50" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="101" t="s">
+      <c r="E50" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="29" t="s">
+      <c r="F50" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="6" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="82"/>
-      <c r="B51" s="107"/>
-      <c r="C51" s="108"/>
-      <c r="D51" s="34" t="s">
+      <c r="A51" s="95"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="96"/>
+      <c r="D51" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E51" s="109"/>
-      <c r="F51" s="35" t="s">
+      <c r="E51" s="89"/>
+      <c r="F51" s="29" t="s">
         <v>286</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="5" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="110" t="s">
+      <c r="A52" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="B52" s="105" t="s">
+      <c r="B52" s="82" t="s">
         <v>315</v>
       </c>
-      <c r="C52" s="113" t="s">
+      <c r="C52" s="77" t="s">
         <v>308</v>
       </c>
-      <c r="D52" s="36" t="s">
+      <c r="D52" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="116" t="s">
+      <c r="E52" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="F52" s="37" t="s">
+      <c r="F52" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="G52" s="11" t="s">
+      <c r="G52" s="7" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="111"/>
-      <c r="B53" s="106"/>
-      <c r="C53" s="114"/>
-      <c r="D53" s="28" t="s">
+      <c r="A53" s="75"/>
+      <c r="B53" s="83"/>
+      <c r="C53" s="78"/>
+      <c r="D53" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E53" s="101"/>
-      <c r="F53" s="29" t="s">
+      <c r="E53" s="81"/>
+      <c r="F53" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="6" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="111"/>
-      <c r="B54" s="106"/>
-      <c r="C54" s="114"/>
-      <c r="D54" s="28" t="s">
+      <c r="A54" s="75"/>
+      <c r="B54" s="83"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="101" t="s">
+      <c r="E54" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="29" t="s">
+      <c r="F54" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" s="6" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="111"/>
-      <c r="B55" s="106"/>
-      <c r="C55" s="114"/>
-      <c r="D55" s="28" t="s">
+      <c r="A55" s="75"/>
+      <c r="B55" s="83"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E55" s="101"/>
-      <c r="F55" s="29" t="s">
+      <c r="E55" s="81"/>
+      <c r="F55" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="6" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="111"/>
-      <c r="B56" s="106"/>
-      <c r="C56" s="114"/>
-      <c r="D56" s="28" t="s">
+      <c r="A56" s="75"/>
+      <c r="B56" s="83"/>
+      <c r="C56" s="78"/>
+      <c r="D56" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E56" s="101" t="s">
+      <c r="E56" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="F56" s="29" t="s">
+      <c r="F56" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="112"/>
-      <c r="B57" s="106"/>
-      <c r="C57" s="115"/>
-      <c r="D57" s="34" t="s">
+      <c r="A57" s="76"/>
+      <c r="B57" s="83"/>
+      <c r="C57" s="79"/>
+      <c r="D57" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E57" s="101"/>
-      <c r="F57" s="35" t="s">
+      <c r="E57" s="81"/>
+      <c r="F57" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="5" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="117" t="s">
+      <c r="A58" s="85" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="106"/>
-      <c r="C58" s="118" t="s">
+      <c r="B58" s="83"/>
+      <c r="C58" s="86" t="s">
         <v>309</v>
       </c>
-      <c r="D58" s="26" t="s">
+      <c r="D58" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="101" t="s">
+      <c r="E58" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="F58" s="27" t="s">
+      <c r="F58" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="111"/>
-      <c r="B59" s="106"/>
-      <c r="C59" s="119"/>
-      <c r="D59" s="28" t="s">
+      <c r="A59" s="75"/>
+      <c r="B59" s="83"/>
+      <c r="C59" s="87"/>
+      <c r="D59" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="101"/>
-      <c r="F59" s="29" t="s">
+      <c r="E59" s="81"/>
+      <c r="F59" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="6" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="111"/>
-      <c r="B60" s="106"/>
-      <c r="C60" s="119"/>
-      <c r="D60" s="28" t="s">
+      <c r="A60" s="75"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="87"/>
+      <c r="D60" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E60" s="101" t="s">
+      <c r="E60" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="F60" s="29" t="s">
+      <c r="F60" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="6" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="111"/>
-      <c r="B61" s="106"/>
-      <c r="C61" s="119"/>
-      <c r="D61" s="28" t="s">
+      <c r="A61" s="75"/>
+      <c r="B61" s="83"/>
+      <c r="C61" s="87"/>
+      <c r="D61" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E61" s="101"/>
-      <c r="F61" s="29" t="s">
+      <c r="E61" s="81"/>
+      <c r="F61" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="G61" s="6" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="111"/>
-      <c r="B62" s="106"/>
-      <c r="C62" s="119"/>
-      <c r="D62" s="28" t="s">
+      <c r="A62" s="75"/>
+      <c r="B62" s="83"/>
+      <c r="C62" s="87"/>
+      <c r="D62" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E62" s="101" t="s">
+      <c r="E62" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="F62" s="29" t="s">
+      <c r="F62" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="G62" s="6" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="112"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="120"/>
-      <c r="D63" s="34" t="s">
+      <c r="A63" s="76"/>
+      <c r="B63" s="84"/>
+      <c r="C63" s="88"/>
+      <c r="D63" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E63" s="109"/>
-      <c r="F63" s="35" t="s">
+      <c r="E63" s="89"/>
+      <c r="F63" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G63" s="5" t="s">
         <v>187</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="C28:C33"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="B28:B33"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="C34:C39"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="B40:B51"/>
+    <mergeCell ref="A46:A51"/>
+    <mergeCell ref="C46:C51"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="E50:E51"/>
     <mergeCell ref="A52:A57"/>
     <mergeCell ref="C52:C57"/>
     <mergeCell ref="E52:E53"/>
@@ -4884,51 +4932,6 @@
     <mergeCell ref="E58:E59"/>
     <mergeCell ref="E60:E61"/>
     <mergeCell ref="E62:E63"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="B40:B51"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="C46:C51"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="B16:B27"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:F13 F37:F57 F15:F35">
     <cfRule type="duplicateValues" dxfId="9" priority="10"/>
